--- a/tests/TC-06/results/teacher_timetables_even.xlsx
+++ b/tests/TC-06/results/teacher_timetables_even.xlsx
@@ -620,30 +620,30 @@
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 102</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 102</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 102</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 102</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
@@ -654,27 +654,9 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
@@ -688,34 +670,10 @@
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
@@ -737,10 +695,34 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -749,17 +731,29 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>CS602 TUT
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
@@ -771,34 +765,10 @@
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
@@ -808,8 +778,20 @@
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>CS602 TUT
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>CS602 TUT
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="T6" s="5" t="inlineStr"/>
       <c r="U6" s="5" t="inlineStr"/>
     </row>
@@ -821,7 +803,13 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>CS603 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
           <t>CS603 LEC
@@ -850,24 +838,24 @@
 Room: 101</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>CS603 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>CS603 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>

--- a/tests/TC-06/results/teacher_timetables_even.xlsx
+++ b/tests/TC-06/results/teacher_timetables_even.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TBD" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TBD_CS601" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TBD_CS602" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TBD_CS603" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -95,10 +97,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -470,6 +472,656 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TBD_CS601  Weekly Timetable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>11:00-11:30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>11:30-12:00</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>12:30-13:15</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>18:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>CS601 LEC
+(CSE_2_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TBD_CS602  Weekly Timetable</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>07:30-09:00</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>09:00-10:00</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>10:00-10:30</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>10:45-11:00</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>11:00-11:30</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>11:30-12:00</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>12:00-12:15</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>12:30-13:15</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>13:15-14:00</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>14:00-14:30</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>14:30-15:30</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>15:30-15:40</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>15:40-16:00</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>16:00-16:30</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>16:30-17:10</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>17:10-17:30</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>17:30-18:30</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>18:30-20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="35" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="35" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>CS602 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="35" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="35" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>CS602 TUT
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>CS602 TUT
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:U1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -498,7 +1150,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TBD  Weekly Timetable</t>
+          <t>TBD_CS603  Weekly Timetable</t>
         </is>
       </c>
     </row>
@@ -618,34 +1270,10 @@
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
       <c r="I3" s="3" t="inlineStr"/>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
@@ -661,31 +1289,31 @@
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr"/>
+      <c r="C4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -694,35 +1322,35 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>CS602 LEC
-(CSE_2_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>CS603 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CS603 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>CS603 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>CS603 LEC
+(CSE_2_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
@@ -731,69 +1359,39 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>CS602 TUT
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="S6" s="6" t="inlineStr">
-        <is>
-          <t>CS602 TUT
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr"/>
+      <c r="U6" s="4" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -803,59 +1401,17 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>CS603 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>CS603 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>CS603 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>CS603 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>CS603 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>CS601 LEC
-(CSE_2_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
